--- a/01SamplePCBProgram/副本无刷跑步机协议.xlsx
+++ b/01SamplePCBProgram/副本无刷跑步机协议.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Huey\BDC\01SamplePCBProgram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E2CC21-29AD-4FF4-8124-48EA0B8857C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292BAF24-EF0A-45AA-AEF0-A12CB28C4E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="420" windowWidth="22308" windowHeight="11820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="新版协议" sheetId="2" r:id="rId2"/>
-    <sheet name="新版协议流程" sheetId="4" r:id="rId3"/>
-    <sheet name="生产报错" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="新版协议" sheetId="2" r:id="rId1"/>
+    <sheet name="新版协议流程" sheetId="4" r:id="rId2"/>
+    <sheet name="生产报错" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="226">
   <si>
     <t>下控——上控通信协议</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -110,10 +109,6 @@
   </si>
   <si>
     <t>0x00</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>档位信息(10代表1.0档位)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -208,10 +203,6 @@
     <t>停止信号</t>
   </si>
   <si>
-    <t>档位指令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0xAA</t>
   </si>
   <si>
@@ -225,23 +216,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>档位指令(10代表1.0档位)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>出厂测试指令</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>0xFF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大档位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最小档位</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -363,14 +342,6 @@
   </si>
   <si>
     <t>启动前馈转速</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>急停指令</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>速度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1476,18 +1447,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1579,7 +1544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1601,7 +1566,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1612,24 +1577,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1665,16 +1614,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1686,47 +1635,35 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2016,901 +1953,46 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="13.88671875" customWidth="1"/>
-    <col min="8" max="8" width="22.5546875" customWidth="1"/>
-    <col min="9" max="9" width="15.77734375" customWidth="1"/>
-    <col min="10" max="10" width="26.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" customWidth="1"/>
-    <col min="12" max="12" width="22.44140625" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" customWidth="1"/>
-    <col min="16" max="16" width="13.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2">
-        <v>4</v>
-      </c>
-      <c r="F2" s="2">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2">
-        <v>6</v>
-      </c>
-      <c r="H2" s="2">
-        <v>7</v>
-      </c>
-      <c r="I2" s="2">
-        <v>8</v>
-      </c>
-      <c r="J2" s="2">
-        <v>9</v>
-      </c>
-      <c r="K2" s="2">
-        <v>10</v>
-      </c>
-      <c r="L2" s="2">
-        <v>11</v>
-      </c>
-      <c r="M2" s="2">
-        <v>12</v>
-      </c>
-      <c r="N2" s="2">
-        <v>13</v>
-      </c>
-      <c r="O2" s="2">
-        <v>14</v>
-      </c>
-      <c r="P2" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>16</v>
-      </c>
-      <c r="R2" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="42"/>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" s="13" customFormat="1" ht="119.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" s="18" customFormat="1" ht="119.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="50"/>
-      <c r="K5" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="L5" s="45"/>
-      <c r="M5" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="222.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="47"/>
-      <c r="I6" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="47"/>
-      <c r="M6" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="47"/>
-      <c r="K7" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="47"/>
-      <c r="M7" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="J8" s="47"/>
-      <c r="K8" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="L8" s="47"/>
-      <c r="M8" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2">
-        <v>4</v>
-      </c>
-      <c r="F11" s="2">
-        <v>5</v>
-      </c>
-      <c r="G11" s="2">
-        <v>6</v>
-      </c>
-      <c r="H11" s="2">
-        <v>7</v>
-      </c>
-      <c r="I11" s="2">
-        <v>8</v>
-      </c>
-      <c r="J11" s="2">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2">
-        <v>10</v>
-      </c>
-      <c r="L11" s="2">
-        <v>11</v>
-      </c>
-      <c r="M11" s="2">
-        <v>12</v>
-      </c>
-      <c r="N11" s="2">
-        <v>13</v>
-      </c>
-      <c r="O11" s="2">
-        <v>14</v>
-      </c>
-      <c r="P11" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>16</v>
-      </c>
-      <c r="R11" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="42"/>
-      <c r="B12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="O13" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="47">
-        <v>0</v>
-      </c>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47">
-        <v>0</v>
-      </c>
-      <c r="J14" s="47"/>
-      <c r="K14" s="7">
-        <v>0</v>
-      </c>
-      <c r="L14" s="7">
-        <v>0</v>
-      </c>
-      <c r="M14" s="7">
-        <v>0</v>
-      </c>
-      <c r="N14" s="7">
-        <v>0</v>
-      </c>
-      <c r="O14" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="48">
-        <v>0</v>
-      </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48">
-        <v>0</v>
-      </c>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48">
-        <v>0</v>
-      </c>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48">
-        <v>0</v>
-      </c>
-      <c r="N15" s="48"/>
-      <c r="O15" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45">
-        <v>0</v>
-      </c>
-      <c r="J16" s="45"/>
-      <c r="K16" s="46">
-        <v>0</v>
-      </c>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46">
-        <v>0</v>
-      </c>
-      <c r="N16" s="46"/>
-      <c r="O16" s="45" t="s">
-        <v>28</v>
-      </c>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="R16" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39">
-        <v>0</v>
-      </c>
-      <c r="J17" s="39"/>
-      <c r="K17" s="43">
-        <v>0</v>
-      </c>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43">
-        <v>0</v>
-      </c>
-      <c r="N17" s="43"/>
-      <c r="O17" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="R17" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18" s="41">
-        <v>0</v>
-      </c>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41">
-        <v>0</v>
-      </c>
-      <c r="J18" s="41"/>
-      <c r="K18" s="41">
-        <v>0</v>
-      </c>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41">
-        <v>0</v>
-      </c>
-      <c r="N18" s="41"/>
-    </row>
-    <row r="19" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="52">
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="A10:R10"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0B893C-5637-4FD6-AAA8-530D00FE3760}">
   <dimension ref="A1:R40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="13.88671875" customWidth="1"/>
-    <col min="8" max="8" width="22.5546875" customWidth="1"/>
+    <col min="8" max="8" width="27" customWidth="1"/>
     <col min="9" max="9" width="15.77734375" customWidth="1"/>
     <col min="10" max="10" width="26.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" customWidth="1"/>
-    <col min="12" max="12" width="22.44140625" customWidth="1"/>
+    <col min="11" max="11" width="19.77734375" customWidth="1"/>
+    <col min="12" max="12" width="24.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
     <col min="15" max="15" width="12.5546875" customWidth="1"/>
     <col min="16" max="16" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
@@ -2966,7 +2048,7 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="42"/>
+      <c r="A3" s="35"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -3019,55 +2101,55 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="18" customFormat="1" ht="119.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:18" s="12" customFormat="1" ht="119.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="45"/>
-      <c r="I4" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="50"/>
-      <c r="K4" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="L4" s="45"/>
-      <c r="M4" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45" t="s">
+      <c r="G4" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="32"/>
+      <c r="I4" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="37"/>
+      <c r="K4" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="L4" s="32"/>
+      <c r="M4" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="17" t="s">
+      <c r="R4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="17" t="s">
+    </row>
+    <row r="5" spans="1:18" ht="214.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="203.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>20</v>
@@ -3084,36 +2166,36 @@
       <c r="F5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="34"/>
+      <c r="I5" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="34"/>
+      <c r="M5" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="47"/>
-      <c r="I5" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="L5" s="47"/>
-      <c r="M5" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47" t="s">
+      <c r="N5" s="34"/>
+      <c r="O5" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
@@ -3122,38 +2204,38 @@
         <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="49" t="s">
+      <c r="G6" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="34"/>
+      <c r="I6" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="I6" s="49" t="s">
+      <c r="J6" s="34"/>
+      <c r="K6" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="47"/>
-      <c r="K6" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="47"/>
-      <c r="M6" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>20</v>
@@ -3162,32 +2244,32 @@
         <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="49" t="s">
+      <c r="G7" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="34"/>
+      <c r="I7" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="49" t="s">
+      <c r="J7" s="34"/>
+      <c r="K7" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="47"/>
-      <c r="K7" s="49" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="47"/>
-      <c r="M7" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
@@ -3198,22 +2280,22 @@
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="21"/>
-      <c r="O8" s="21"/>
-      <c r="P8" s="21"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>20</v>
@@ -3222,38 +2304,38 @@
         <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="49" t="s">
+      <c r="G9" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49" t="s">
+      <c r="L9" s="33"/>
+      <c r="M9" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="N9" s="49"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>20</v>
@@ -3262,38 +2344,38 @@
         <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="N10" s="49"/>
-      <c r="O10" s="21"/>
-      <c r="P10" s="21"/>
+      <c r="G10" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="33"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>20</v>
@@ -3302,38 +2384,38 @@
         <v>21</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="L11" s="49"/>
-      <c r="M11" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="N11" s="49"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
+      <c r="G11" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="N11" s="33"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>20</v>
@@ -3342,38 +2424,38 @@
         <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="N12" s="49"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
+        <v>51</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="N12" s="33"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>20</v>
@@ -3382,38 +2464,38 @@
         <v>21</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G13" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="N13" s="49"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
+        <v>86</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="N13" s="33"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -3422,38 +2504,38 @@
         <v>21</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G14" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="N14" s="49"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
+        <v>128</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="N14" s="33"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>20</v>
@@ -3462,53 +2544,53 @@
         <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="N15" s="49"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
+        <v>129</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="N15" s="33"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G16" s="41">
         <v>0</v>
@@ -3534,16 +2616,16 @@
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
@@ -3554,23 +2636,23 @@
       <c r="D18" s="2"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="49" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="49"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="33"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="35" t="s">
         <v>1</v>
       </c>
       <c r="B19" s="2">
@@ -3626,7 +2708,7 @@
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="42"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
@@ -3681,7 +2763,7 @@
     </row>
     <row r="21" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>20</v>
@@ -3690,7 +2772,7 @@
         <v>21</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>23</v>
@@ -3699,43 +2781,43 @@
         <v>24</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="O21" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="O21" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>20</v>
@@ -3744,22 +2826,22 @@
         <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="47">
-        <v>0</v>
-      </c>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47">
-        <v>0</v>
-      </c>
-      <c r="J22" s="47"/>
+      <c r="G22" s="34">
+        <v>0</v>
+      </c>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34">
+        <v>0</v>
+      </c>
+      <c r="J22" s="34"/>
       <c r="K22" s="7">
         <v>0</v>
       </c>
@@ -3772,20 +2854,20 @@
       <c r="N22" s="7">
         <v>0</v>
       </c>
-      <c r="O22" s="47" t="s">
+      <c r="O22" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>20</v>
@@ -3794,105 +2876,105 @@
         <v>21</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="48">
-        <v>0</v>
-      </c>
-      <c r="H23" s="48"/>
-      <c r="I23" s="48">
-        <v>0</v>
-      </c>
-      <c r="J23" s="48"/>
-      <c r="K23" s="48">
-        <v>0</v>
-      </c>
-      <c r="L23" s="48"/>
-      <c r="M23" s="48">
-        <v>0</v>
-      </c>
-      <c r="N23" s="48"/>
-      <c r="O23" s="47" t="s">
+      <c r="G23" s="39">
+        <v>0</v>
+      </c>
+      <c r="H23" s="39"/>
+      <c r="I23" s="39">
+        <v>0</v>
+      </c>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39">
+        <v>0</v>
+      </c>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39">
+        <v>0</v>
+      </c>
+      <c r="N23" s="39"/>
+      <c r="O23" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="R23" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" s="18" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="15" t="s">
+    </row>
+    <row r="24" spans="1:18" s="12" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="E24" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45">
-        <v>0</v>
-      </c>
-      <c r="J24" s="45"/>
-      <c r="K24" s="46">
-        <v>0</v>
-      </c>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46">
-        <v>0</v>
-      </c>
-      <c r="N24" s="46"/>
-      <c r="O24" s="45" t="s">
+      <c r="G24" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32">
+        <v>0</v>
+      </c>
+      <c r="J24" s="32"/>
+      <c r="K24" s="40">
+        <v>0</v>
+      </c>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40">
+        <v>0</v>
+      </c>
+      <c r="N24" s="40"/>
+      <c r="O24" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="17" t="s">
+      <c r="R24" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="R24" s="17" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E25" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G25" s="41">
         <v>0</v>
@@ -3913,19 +2995,19 @@
     </row>
     <row r="26" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>23</v>
@@ -3957,22 +3039,22 @@
     </row>
     <row r="27" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4001,22 +3083,22 @@
     </row>
     <row r="28" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -4045,22 +3127,22 @@
     </row>
     <row r="29" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4089,22 +3171,22 @@
     </row>
     <row r="30" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4133,22 +3215,22 @@
     </row>
     <row r="31" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E31" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4177,22 +3259,22 @@
     </row>
     <row r="32" spans="1:18" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4221,255 +3303,255 @@
     </row>
     <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G33" s="49" t="s">
+      <c r="G33" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49" t="s">
+      <c r="L33" s="33"/>
+      <c r="M33" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="J33" s="49"/>
-      <c r="K33" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="L33" s="49"/>
-      <c r="M33" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="N33" s="49"/>
+      <c r="N33" s="33"/>
     </row>
     <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49" t="s">
-        <v>101</v>
-      </c>
-      <c r="J34" s="49"/>
-      <c r="K34" s="49" t="s">
-        <v>102</v>
-      </c>
-      <c r="L34" s="49"/>
-      <c r="M34" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="N34" s="49"/>
+        <v>34</v>
+      </c>
+      <c r="G34" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="N34" s="33"/>
     </row>
     <row r="35" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="E35" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G35" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="L35" s="49"/>
-      <c r="M35" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="N35" s="49"/>
+      <c r="G35" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="N35" s="33"/>
     </row>
     <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G36" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49" t="s">
-        <v>110</v>
-      </c>
-      <c r="L36" s="49"/>
-      <c r="M36" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="N36" s="49"/>
+        <v>86</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="N36" s="33"/>
     </row>
     <row r="37" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G37" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="L37" s="49"/>
-      <c r="M37" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="N37" s="49"/>
+        <v>128</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="L37" s="33"/>
+      <c r="M37" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="N37" s="33"/>
     </row>
     <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G38" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="L38" s="49"/>
-      <c r="M38" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="N38" s="49"/>
+        <v>129</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33" t="s">
+        <v>112</v>
+      </c>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="L38" s="33"/>
+      <c r="M38" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="N38" s="33"/>
     </row>
     <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="G39" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="L39" s="49"/>
-      <c r="M39" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="N39" s="49"/>
+        <v>130</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="N39" s="33"/>
     </row>
     <row r="40" spans="1:14" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
@@ -4481,33 +3563,57 @@
     </row>
   </sheetData>
   <mergeCells count="102">
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="O21:P21"/>
     <mergeCell ref="G22:H22"/>
@@ -4532,57 +3638,33 @@
     <mergeCell ref="K10:L10"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4590,7 +3672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0713B187-A411-44D5-8FEF-705CC0176FFB}">
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -4600,10 +3682,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4611,7 +3693,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C2">
         <v>1E-3</v>
@@ -4622,7 +3704,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C3">
         <v>1.0000000000000001E-5</v>
@@ -4633,7 +3715,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>1.0000000000000001E-5</v>
@@ -4644,7 +3726,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>0.01</v>
@@ -4655,7 +3737,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>1.0000000000000001E-5</v>
@@ -4666,7 +3748,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>0.01</v>
@@ -4677,7 +3759,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C8">
         <v>0.01</v>
@@ -4688,7 +3770,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C9">
         <v>1.0000000000000001E-5</v>
@@ -4699,7 +3781,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C10">
         <v>0.01</v>
@@ -4710,7 +3792,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C11">
         <v>0.01</v>
@@ -4721,7 +3803,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C12">
         <v>1.0000000000000001E-5</v>
@@ -4732,7 +3814,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>0.01</v>
@@ -4743,7 +3825,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C14">
         <v>0.01</v>
@@ -4754,7 +3836,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C15">
         <v>1.0000000000000001E-5</v>
@@ -4765,7 +3847,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C16">
         <v>0.01</v>
@@ -4776,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -4787,7 +3869,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -4798,7 +3880,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C19">
         <v>1E-3</v>
@@ -4809,7 +3891,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C20">
         <v>1E-3</v>
@@ -4820,7 +3902,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C21">
         <v>1E-3</v>
@@ -4831,7 +3913,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C22">
         <v>0.01</v>
@@ -4842,7 +3924,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C23">
         <v>0.01</v>
@@ -4853,7 +3935,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C24">
         <v>0.01</v>
@@ -4864,7 +3946,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -4875,7 +3957,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C26">
         <v>0.01</v>
@@ -4887,7 +3969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C47F6C-EEEB-42B6-B256-598749354F11}">
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -4898,235 +3980,235 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="31"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="37"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="C2" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C2" s="22" t="s">
+      <c r="B5" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="C5" s="16" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="C3" s="22" t="s">
+      <c r="D5" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="D3" s="23" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B6" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C6" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
+      <c r="D6" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="22" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="B7" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="C7" s="16" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="D7" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="B6" s="22" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="B8" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="C8" s="16" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="D8" s="17" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B9" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C9" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D9" s="17" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B10" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C10" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="D10" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="22" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="B11" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="C11" s="16" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="D11" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B12" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C12" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D12" s="17" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B13" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C13" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="D13" s="18" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B14" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C14" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D14" s="21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="23" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="B15" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="C15" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="B16" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="C16" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="D16" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="C14" s="26" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="D14" s="27" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+      <c r="B17" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="C17" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C15" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="D17" s="17" t="s">
         <v>196</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
-        <v>200</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -5139,7 +4221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63F2F0A9-FC3C-4F2A-806C-0ACED4FEAD6A}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -5150,76 +4232,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="23.4" x14ac:dyDescent="0.5">
-      <c r="A1" s="52" t="s">
-        <v>228</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="54"/>
+      <c r="A1" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="44"/>
     </row>
     <row r="2" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="58.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="C2" s="34" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="58.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="B3" s="32" t="s">
+      <c r="C5" s="25" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="B6" s="27" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="43.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="C6" s="25" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B7" s="27" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="B6" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>215</v>
+      <c r="C7" s="25" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
